--- a/docs/Mapping_casi_uso/matrimoni/Matr_005.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_005.xlsx
@@ -6067,7 +6067,7 @@
         <v>94</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>192</v>
@@ -6182,7 +6182,7 @@
         <v>104</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>192</v>
@@ -6297,7 +6297,7 @@
         <v>114</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>192</v>
@@ -6343,7 +6343,7 @@
         <v>118</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>192</v>
@@ -6366,7 +6366,7 @@
         <v>120</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>192</v>
@@ -6412,7 +6412,7 @@
         <v>124</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>192</v>
@@ -6435,7 +6435,7 @@
         <v>126</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>192</v>
@@ -6458,7 +6458,7 @@
         <v>128</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>192</v>
@@ -6504,7 +6504,7 @@
         <v>132</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>192</v>
@@ -6550,7 +6550,7 @@
         <v>136</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>192</v>
@@ -6596,7 +6596,7 @@
         <v>140</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>192</v>
@@ -6619,7 +6619,7 @@
         <v>142</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>192</v>
@@ -6711,7 +6711,7 @@
         <v>94</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>195</v>
@@ -6826,7 +6826,7 @@
         <v>104</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G243" s="2" t="s">
         <v>195</v>
@@ -6941,7 +6941,7 @@
         <v>114</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>195</v>
@@ -6987,7 +6987,7 @@
         <v>118</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>195</v>
@@ -7010,7 +7010,7 @@
         <v>120</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>195</v>
@@ -7056,7 +7056,7 @@
         <v>124</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>195</v>
@@ -7079,7 +7079,7 @@
         <v>126</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>195</v>
@@ -7102,7 +7102,7 @@
         <v>128</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>195</v>
@@ -7148,7 +7148,7 @@
         <v>132</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>195</v>
@@ -7194,7 +7194,7 @@
         <v>136</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>195</v>
@@ -7240,7 +7240,7 @@
         <v>140</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>195</v>
@@ -7263,7 +7263,7 @@
         <v>142</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>195</v>
